--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>SPECIAL NOTICES (-30)</t>
+  </si>
+  <si>
+    <t>ArCcpcStatements3492.paragraphCodes</t>
+  </si>
+  <si>
+    <t>PARAGRAPH CODES (-40)</t>
   </si>
   <si>
     <t>ArCcpcStatements3492.patientName</t>
@@ -615,11 +621,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.57421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.54296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.54296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -649,7 +655,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="36.57421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.54296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1765,6 +1771,106 @@
         <v>72</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file AR CCPC STATEMENTS (349.2)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source AR CCPC STATEMENTS (349.2)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="94">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,28 +292,6 @@
   </si>
   <si>
     <t>NEW BALANCE (-.08)</t>
-  </si>
-  <si>
-    <t>ArCcpcStatements3492.pdLine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/PdLine34921)
-</t>
-  </si>
-  <si>
-    <t>PD LINE (-20)</t>
-  </si>
-  <si>
-    <t>ArCcpcStatements3492.specialNotices</t>
-  </si>
-  <si>
-    <t>SPECIAL NOTICES (-30)</t>
-  </si>
-  <si>
-    <t>ArCcpcStatements3492.paragraphCodes</t>
-  </si>
-  <si>
-    <t>PARAGRAPH CODES (-40)</t>
   </si>
   <si>
     <t>ArCcpcStatements3492.patientName</t>
@@ -621,11 +599,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.54296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.54296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -634,7 +612,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="57.8984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="57.78125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -655,7 +633,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.54296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1499,13 +1477,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="M9" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1568,306 +1546,6 @@
         <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-ArCcpcStatements3492.xlsx
+++ b/docs/StructureDefinition-ArCcpcStatements3492.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
